--- a/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:59</t>
+          <t>2026-09-29 01:01:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:01</t>
+          <t>2026-09-29 01:01:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:02</t>
+          <t>2026-09-29 01:01:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:03</t>
+          <t>2026-09-29 01:01:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:03</t>
+          <t>2026-09-29 01:01:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:03</t>
+          <t>2026-09-29 01:01:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:03</t>
+          <t>2026-09-29 01:01:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 00:54:03</t>
+          <t>2026-09-29 01:01:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:53</t>
+          <t>2026-09-29 01:40:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:54</t>
+          <t>2026-09-29 01:40:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:55</t>
+          <t>2026-09-29 01:40:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:57</t>
+          <t>2026-09-29 01:40:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.95%870,000</t>
+          <t>9.16%870,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>9.16%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.19%282,000</t>
+          <t>5.89%282,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.19%</t>
+          <t>5.89%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3555</v>
+        <v>1165</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.80%393,000</t>
+          <t>5.70%1,150,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.70%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>393000</v>
+        <v>1150000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1185</v>
+        <v>3400</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.66%1,150,000</t>
+          <t>5.69%393,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>5.69%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1150000</v>
+        <v>393000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8525</v>
+        <v>4920</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.07%143,000</t>
+          <t>4.94%236,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>143000</v>
+        <v>236000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5050</v>
+        <v>7925</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.95%236,000</t>
+          <t>4.82%143,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>236000</v>
+        <v>143000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.68%418,644</t>
+          <t>3.74%418,644</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6920</v>
+        <v>6895</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.51%122,000</t>
+          <t>3.58%122,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.51%565,000</t>
+          <t>3.57%565,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.90%998,000</t>
+          <t>2.92%998,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5415</v>
+        <v>12115</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.70%120,000</t>
+          <t>2.68%52,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>120000</v>
+        <v>52000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1910</v>
+        <v>1835</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.69%339,000</t>
+          <t>2.65%339,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>12350</v>
+        <v>5185</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.67%52,000</t>
+          <t>2.65%120,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>52000</v>
+        <v>120000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19835</v>
+        <v>19395</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:46</t>
+          <t>2026-09-29 22:56:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1895</v>
+        <v>1810</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.54%322,000</t>
+          <t>2.48%322,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.48%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.22%580</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>580</v>
+        <v>2445</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.26%939,000</t>
+          <t>2.35%226,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>939000</v>
+        <v>226000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>-0.59%2515</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2340</v>
+        <v>2515</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.20%226,000</t>
+          <t>2.22%207,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>226000</v>
+        <v>207000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.69%2530</t>
+          <t>-5.52%548</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>-5.52%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2530</v>
+        <v>548</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.18%207,000</t>
+          <t>2.19%939,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>207000</v>
+        <v>939000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.65%1530</t>
+          <t>+3.59%1585</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1530</v>
+        <v>1585</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.06%324,000</t>
+          <t>2.19%324,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.83%356,000</t>
+          <t>1.92%356,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.29%2295</t>
+          <t>-4.79%2185</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-4.79%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2295</v>
+        <v>2185</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.81%190,000</t>
+          <t>1.77%190,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.23%287</t>
+          <t>+9.62%1310</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>+9.62%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>287</v>
+        <v>1310</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.45%1,216,000</t>
+          <t>1.49%267,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1216000</v>
+        <v>267000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.89%6245</t>
+          <t>-2.09%281</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6245</v>
+        <v>281</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.43%55,000</t>
+          <t>1.45%1,216,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>55000</v>
+        <v>1216000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-4.75%3310</t>
+          <t>-3.6%6020</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3310</v>
+        <v>6020</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.38%100,000</t>
+          <t>1.41%55,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>100000</v>
+        <v>55000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.75%2700</t>
+          <t>-1.85%2650</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.75%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.33%119,000</t>
+          <t>1.34%119,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.83%1195</t>
+          <t>-5.14%3140</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1195</v>
+        <v>3140</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.33%267,000</t>
+          <t>1.34%100,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>267000</v>
+        <v>100000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.68%971</t>
+          <t>-1.54%956</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.68%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>971</v>
+        <v>956</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.03%255,000</t>
+          <t>1.04%255,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.33%503</t>
+          <t>+0.6%506</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.93%447,000</t>
+          <t>0.96%447,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.64%1555</t>
+          <t>+4.84%498.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+4.84%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1555</v>
+        <v>498.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.92%142,000</t>
+          <t>0.93%438,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>142000</v>
+        <v>438000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:47</t>
+          <t>2026-09-29 22:56:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.53%475.5</t>
+          <t>-2.89%1510</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>475.5</v>
+        <v>1510</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.87%438,000</t>
+          <t>0.91%142,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>438000</v>
+        <v>142000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.9%2410</t>
+          <t>+2.7%2475</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.9%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2410</v>
+        <v>2475</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.84%84,000</t>
+          <t>0.88%84,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+4.62%238</t>
+          <t>+3.78%247</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+4.62%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.72%729,000</t>
+          <t>0.77%729,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.37%543</t>
+          <t>-0.55%540</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.72%317,000</t>
+          <t>0.73%317,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.5%184.5</t>
+          <t>+0.54%185.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>184.5</v>
+        <v>185.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.71%921,000</t>
+          <t>0.73%921,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2615萬海</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.76%115.5</t>
+          <t>+2.32%3305</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>115.5</v>
+        <v>3305</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.68%1,415,000</t>
+          <t>0.70%50,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1415000</v>
+        <v>50000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2615萬海</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.27%3230</t>
+          <t>-3.9%111</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3230</v>
+        <v>111</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.67%50,000</t>
+          <t>0.67%1,415,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>50000</v>
+        <v>1415000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.59%921,000</t>
+          <t>0.60%921,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+4.39%761</t>
+          <t>+2.37%779</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>761</v>
+        <v>779</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.57%179,000</t>
+          <t>0.59%179,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.07%1105</t>
+          <t>+1.36%1120</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.55%119,000</t>
+          <t>0.57%119,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2451創見</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.61%993</t>
+          <t>+0.53%286</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>993</v>
+        <v>286</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.33%81,000</t>
+          <t>0.32%264,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>81000</v>
+        <v>264000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0%1305</t>
+          <t>-1.92%1280</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1305</v>
+        <v>1280</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-4.06%2125</t>
+          <t>+3.46%1195</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2125</v>
+        <v>1195</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.32%36,000</t>
+          <t>0.32%62,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>36000</v>
+        <v>62000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2451創見</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%284.5</t>
+          <t>-6.45%929</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-6.45%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>284.5</v>
+        <v>929</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.31%264,000</t>
+          <t>0.32%81,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>264000</v>
+        <v>81000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.7%1155</t>
+          <t>-0.47%2115</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1155</v>
+        <v>2115</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.30%62,000</t>
+          <t>0.32%36,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>62000</v>
+        <v>36000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:49</t>
+          <t>2026-09-29 22:56:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.31%378</t>
+          <t>-0.26%377</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:50</t>
+          <t>2026-09-29 22:56:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.58%749</t>
+          <t>+1.47%760</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.22%72,000</t>
+          <t>0.23%72,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:50</t>
+          <t>2026-09-29 22:56:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%542</t>
+          <t>-0.37%540</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:50</t>
+          <t>2026-09-29 22:56:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.58%171.5</t>
+          <t>+1.46%174</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>171.5</v>
+        <v>174</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.13%187,000</t>
+          <t>0.14%187,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:50</t>
+          <t>2026-09-29 22:56:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.63%1210</t>
+          <t>0%1210</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:50</t>
+          <t>2026-09-29 22:56:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.34%145</t>
+          <t>-0.69%144</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:21</t>
+          <t>2026-09-29 23:07:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:22</t>
+          <t>2026-09-29 23:07:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:23</t>
+          <t>2026-09-29 23:07:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:25</t>
+          <t>2026-09-29 23:07:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:25</t>
+          <t>2026-09-29 23:07:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:25</t>
+          <t>2026-09-29 23:07:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:25</t>
+          <t>2026-09-29 23:07:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:25</t>
+          <t>2026-09-29 23:07:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:19</t>
+          <t>2026-09-29 23:52:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:20</t>
+          <t>2026-09-29 23:52:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:22</t>
+          <t>2026-09-29 23:52:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:23</t>
+          <t>2026-09-29 23:52:29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:23</t>
+          <t>2026-09-29 23:52:29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:23</t>
+          <t>2026-09-29 23:52:29</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:23</t>
+          <t>2026-09-29 23:52:29</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:23</t>
+          <t>2026-09-29 23:52:29</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
